--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -259,7 +259,7 @@
     <t>薬の服用方法・服用した方法、または服用すべき方法</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -321,7 +321,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -474,18 +474,19 @@
 </t>
   </si>
   <si>
-    <t>投与日時</t>
-  </si>
-  <si>
-    <t>複数回発生する可能性のあるイベントの発生について説明します。タイミングスケジュールは、イベントが発生することが予想または要求される時期を指定するために使用され、過去または進行中のイベントの概要を表すためにも使用できます。簡単にするために、タイミングコンポーネントの定義は「将来の」イベントとして表現されますが、そのようなコンポーネントは歴史的または進行中のイベントを説明するためにも使用できます。
-タイミングスケジュールは、イベントが発生したときのイベントおよび/または基準のリストであり、構造化された形式またはコードとして表現できます。イベントと繰り返し仕様の両方が提供される場合、イベントのリストは、繰り返し構造の情報の解釈として理解されるべきです。 / Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
-A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+    <t>薬を投与する必要がある場合 / When medication should be administered</t>
+  </si>
+  <si>
+    <t>薬を投与する必要がある場合。 / When medication should be administered.</t>
+  </si>
+  <si>
+    <t>この属性は、Dosage.Textが入力されると予想される間、常に埋め込まれるとは限りません。両方が入力されている場合、Dosage.textはDosage.timingの内容を反映する必要があります。 / This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
   </si>
   <si>
     <t>患者に薬を与えるためのタイミングスケジュール。このデータ型により、さまざまな式が可能になります。たとえば、「8時間ごと」。"一日に三回";「2011年12月23日から10日間の朝食の1/2の1/2：」;「2013年10月15日、2013年10月17日、2013年11月1日」。時には、総量 /持続時間として表される場合、レートは期間を意味する場合があります（たとえば、500ml / 2時間は2時間の期間を意味します）。ただし、レートが期間（250ml/hour）を意味しない場合、期間にわたって注入を伝えるためにタイミング.repeat.durationが必要です。 / The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
-    <t>QSET&lt;TS&gt; (GTS)</t>
+    <t>.effectiveTime</t>
   </si>
   <si>
     <t>Dosage.timing.id</t>
@@ -538,7 +539,7 @@
     <t>Timing.repeat</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
@@ -1204,7 +1205,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1324,7 +1325,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1339,7 +1340,7 @@
     <t>Dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.version</t>
@@ -1419,18 +1420,7 @@
     <t>1つの投与イベントで与えられた治療またはその他の物質の量。 / The amount of therapeutic or other substance given at one administration event.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>RXO-2, RXE-3</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.rate[x]</t>
@@ -1475,19 +1465,6 @@
 </t>
   </si>
   <si>
-    <t>１日当たりでの薬剤の投入量</t>
-  </si>
-  <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.rate[x]:rateRange</t>
   </si>
   <si>
@@ -1498,22 +1475,6 @@
 </t>
   </si>
   <si>
-    <t>範囲指定された時間の上限下限</t>
-  </si>
-  <si>
-    <t>時間の上限量、下限量の範囲を持っている。単位指定された数量を割り当てている。Low,Highの値は時間の単位当てはめる。</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>IVL&lt;QTY[not(type="TS")]&gt; [lowClosed="true" and highClosed="true"]or URG&lt;QTY[not(type="TS")]&gt;</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.rate[x]:rateQuantity</t>
   </si>
   <si>
@@ -1527,9 +1488,6 @@
     <t>投与速度(量/時間)を指定する</t>
   </si>
   <si>
-    <t>使用のコンテキストは、これがどのような量であるか、したがってどのようなユニットを使用できるかを頻繁に定義する場合があります。使用のコンテキストは、コンパレータの値を制限する場合もあります。 / The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
@@ -1540,19 +1498,31 @@
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、「4時間ごとに最大8時間あたり2錠」。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
     <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
+    <t>.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>RXO-23, RXE-19</t>
+  </si>
+  <si>
     <t>Dosage.maxDosePerAdministration</t>
   </si>
   <si>
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、5〜10分間で1.5 mg/m2（最大2 mg）IVなどの最大量の体積領域に関連する用量に関連する用量は、1.5 mg/m2、最大2 mgのDosequantityになります。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
   </si>
   <si>
     <t>投与ごとの被験者に投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>not supported</t>
   </si>
   <si>
     <t>Dosage.maxDosePerLifetime</t>
@@ -3130,7 +3100,7 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>147</v>
@@ -3139,13 +3109,13 @@
         <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3209,18 +3179,18 @@
         <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3323,10 +3293,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3431,10 +3401,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3541,10 +3511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3567,17 +3537,17 @@
         <v>113</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3626,7 +3596,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3641,7 +3611,7 @@
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3649,10 +3619,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3675,17 +3645,17 @@
         <v>113</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3734,7 +3704,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3746,10 +3716,10 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3757,10 +3727,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3863,10 +3833,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3971,10 +3941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3997,13 +3967,13 @@
         <v>113</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4042,7 +4012,7 @@
         <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
@@ -4052,7 +4022,7 @@
         <v>98</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4067,7 +4037,7 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -4075,13 +4045,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>76</v>
@@ -4103,13 +4073,13 @@
         <v>113</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4160,7 +4130,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4175,7 +4145,7 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -4183,10 +4153,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4289,10 +4259,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4397,10 +4367,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4423,19 +4393,19 @@
         <v>113</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4484,7 +4454,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4499,18 +4469,18 @@
         <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4533,23 +4503,23 @@
         <v>113</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R25" t="s" s="2">
         <v>76</v>
@@ -4570,13 +4540,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4594,7 +4564,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4609,18 +4579,18 @@
         <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4646,21 +4616,21 @@
         <v>85</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>76</v>
@@ -4702,7 +4672,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4717,18 +4687,18 @@
         <v>81</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4751,24 +4721,24 @@
         <v>113</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>76</v>
@@ -4810,7 +4780,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4819,24 +4789,24 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4859,26 +4829,26 @@
         <v>113</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>76</v>
@@ -4920,7 +4890,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4935,18 +4905,18 @@
         <v>81</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4969,19 +4939,19 @@
         <v>113</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -5030,7 +5000,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5045,7 +5015,7 @@
         <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -5053,10 +5023,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5079,16 +5049,16 @@
         <v>113</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5138,7 +5108,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5153,7 +5123,7 @@
         <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -5161,10 +5131,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5187,19 +5157,19 @@
         <v>113</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5248,7 +5218,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5263,7 +5233,7 @@
         <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5271,10 +5241,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5297,19 +5267,19 @@
         <v>113</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5358,7 +5328,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5373,7 +5343,7 @@
         <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -5381,10 +5351,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5407,13 +5377,13 @@
         <v>113</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>145</v>
@@ -5442,13 +5412,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5466,7 +5436,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5481,7 +5451,7 @@
         <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5489,10 +5459,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5515,23 +5485,23 @@
         <v>113</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="R34" t="s" s="2">
         <v>76</v>
@@ -5576,7 +5546,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5591,7 +5561,7 @@
         <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5599,10 +5569,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5625,16 +5595,16 @@
         <v>113</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5684,7 +5654,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5699,7 +5669,7 @@
         <v>81</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5707,10 +5677,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5733,16 +5703,16 @@
         <v>113</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5792,7 +5762,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5807,7 +5777,7 @@
         <v>81</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5815,10 +5785,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5841,16 +5811,16 @@
         <v>113</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5900,7 +5870,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5915,7 +5885,7 @@
         <v>81</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5923,10 +5893,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5949,13 +5919,13 @@
         <v>113</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>145</v>
@@ -5984,13 +5954,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -6008,7 +5978,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6023,7 +5993,7 @@
         <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -6031,10 +6001,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6057,16 +6027,16 @@
         <v>113</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6092,11 +6062,11 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -6114,7 +6084,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6137,10 +6107,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6163,16 +6133,16 @@
         <v>113</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6222,7 +6192,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6245,10 +6215,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6271,19 +6241,19 @@
         <v>113</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6308,13 +6278,13 @@
         <v>76</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>76</v>
@@ -6332,7 +6302,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6347,7 +6317,7 @@
         <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6355,10 +6325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6381,16 +6351,16 @@
         <v>113</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6440,7 +6410,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6455,7 +6425,7 @@
         <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6463,10 +6433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6492,13 +6462,13 @@
         <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6528,7 +6498,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>76</v>
@@ -6546,7 +6516,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6561,7 +6531,7 @@
         <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6569,10 +6539,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6595,16 +6565,16 @@
         <v>113</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6654,7 +6624,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6669,18 +6639,18 @@
         <v>81</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6706,16 +6676,16 @@
         <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6744,7 +6714,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6762,7 +6732,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6777,18 +6747,18 @@
         <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6814,16 +6784,16 @@
         <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6852,7 +6822,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>76</v>
@@ -6870,7 +6840,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6885,18 +6855,18 @@
         <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6922,16 +6892,16 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6956,13 +6926,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6980,7 +6950,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6995,18 +6965,18 @@
         <v>81</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7109,10 +7079,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7217,10 +7187,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7243,19 +7213,19 @@
         <v>113</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7292,7 +7262,7 @@
         <v>76</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7302,7 +7272,7 @@
         <v>98</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7317,21 +7287,21 @@
         <v>81</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
@@ -7353,19 +7323,19 @@
         <v>113</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -7394,7 +7364,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7412,7 +7382,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7427,18 +7397,18 @@
         <v>81</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7541,10 +7511,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7649,10 +7619,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7675,26 +7645,26 @@
         <v>113</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>76</v>
@@ -7736,7 +7706,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7751,18 +7721,18 @@
         <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7788,13 +7758,13 @@
         <v>85</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7844,7 +7814,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7859,18 +7829,18 @@
         <v>81</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7893,17 +7863,17 @@
         <v>113</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7952,7 +7922,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7967,18 +7937,18 @@
         <v>81</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8004,14 +7974,14 @@
         <v>85</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8060,7 +8030,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8075,18 +8045,18 @@
         <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8109,19 +8079,19 @@
         <v>113</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8170,7 +8140,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8185,21 +8155,21 @@
         <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>76</v>
@@ -8221,19 +8191,19 @@
         <v>113</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8262,7 +8232,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -8280,7 +8250,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8295,18 +8265,18 @@
         <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8409,10 +8379,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8517,10 +8487,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8543,26 +8513,26 @@
         <v>113</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>76</v>
@@ -8604,7 +8574,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8619,18 +8589,18 @@
         <v>81</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8656,13 +8626,13 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8712,7 +8682,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8727,18 +8697,18 @@
         <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8761,17 +8731,17 @@
         <v>113</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8820,7 +8790,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8835,18 +8805,18 @@
         <v>81</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8872,14 +8842,14 @@
         <v>85</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8928,7 +8898,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8943,18 +8913,18 @@
         <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8977,19 +8947,19 @@
         <v>113</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9038,7 +9008,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9053,18 +9023,18 @@
         <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9148,7 +9118,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9163,18 +9133,18 @@
         <v>81</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9197,13 +9167,13 @@
         <v>113</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9254,7 +9224,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9272,15 +9242,15 @@
         <v>76</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9383,10 +9353,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9491,10 +9461,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9520,16 +9490,16 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>76</v>
@@ -9558,7 +9528,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>76</v>
@@ -9576,7 +9546,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9594,15 +9564,15 @@
         <v>76</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9622,22 +9592,22 @@
         <v>76</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9686,7 +9656,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9695,24 +9665,24 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9735,19 +9705,19 @@
         <v>113</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9784,17 +9754,17 @@
         <v>76</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC73" s="2"/>
       <c r="AD73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9809,21 +9779,21 @@
         <v>81</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>76</v>
@@ -9842,22 +9812,22 @@
         <v>76</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -9906,7 +9876,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -9915,27 +9885,27 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>118</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>76</v>
@@ -9954,22 +9924,22 @@
         <v>76</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -10018,7 +9988,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10027,27 +9997,27 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>482</v>
+        <v>465</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>76</v>
@@ -10066,22 +10036,22 @@
         <v>76</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -10130,7 +10100,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10139,24 +10109,24 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>456</v>
+        <v>81</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10176,22 +10146,22 @@
         <v>76</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>76</v>
@@ -10240,7 +10210,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10249,24 +10219,24 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>118</v>
+        <v>482</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10286,22 +10256,22 @@
         <v>76</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10350,7 +10320,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10359,24 +10329,24 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>456</v>
+        <v>81</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>458</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10396,22 +10366,20 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10460,7 +10428,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10469,16 +10437,16 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>456</v>
+        <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>458</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -635,7 +635,7 @@
 </t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -650,7 +650,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
@@ -1838,17 +1838,17 @@
   <dimension ref="A1:AL79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.37109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.0625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.18359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.05859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.27734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1857,24 +1857,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="104.59765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.11328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
@@ -1107,7 +1107,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1427,7 +1427,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
